--- a/data/supplementary_information/4.SAP_BLUE_traits_plotted_HN_LN_NR.xlsx
+++ b/data/supplementary_information/4.SAP_BLUE_traits_plotted_HN_LN_NR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/subhashmahamkali/Documents/gwas_sap/data/supplementary_information/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10CB37B0-7645-814B-928B-ACE5FDB0EA34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6537A3FE-2A01-E944-8B9B-F6762E44FB45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="620" windowWidth="27040" windowHeight="15900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1613" uniqueCount="409">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1614" uniqueCount="410">
   <si>
     <t>genotype</t>
   </si>
@@ -1248,13 +1248,24 @@
   <si>
     <t>NA</t>
   </si>
+  <si>
+    <t>Table S2. BLUE values for phenotypic traits measured under high N, low N, and N response conditions in the Sorghum</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
@@ -1282,8 +1293,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1580,7 +1594,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:BI349"/>
+  <dimension ref="A1:BI349"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.6640625" customWidth="1"/>
@@ -1618,6 +1632,14 @@
     <col min="60" max="61" width="25.6640625" customWidth="1"/>
   </cols>
   <sheetData>
+    <row r="1" spans="1:61" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+    </row>
     <row r="2" spans="1:61" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>0</v>
@@ -65999,6 +66021,9 @@
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:D1"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
